--- a/Result/profitability/1410.xlsx
+++ b/Result/profitability/1410.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.105</v>
       </c>
       <c r="N2" t="n">
-        <v>28.56</v>
+        <v>28.63</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07375</v>
+        <v>0.0675</v>
       </c>
       <c r="N3" t="n">
-        <v>27.17</v>
+        <v>27.47375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08125</v>
+        <v>0.08375</v>
       </c>
       <c r="N4" t="n">
-        <v>25.57625</v>
+        <v>25.82125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07375</v>
+        <v>0.0975</v>
       </c>
       <c r="N5" t="n">
-        <v>22.9275</v>
+        <v>23.625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07375000000000001</v>
+        <v>0.0325</v>
       </c>
       <c r="N6" t="n">
-        <v>19.8225</v>
+        <v>22.5575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002500000000000002</v>
+        <v>-0.006250000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>20.5825</v>
+        <v>21.28875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0075</v>
+        <v>0.01625</v>
       </c>
       <c r="N8" t="n">
-        <v>19.89875</v>
+        <v>20.63875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00375</v>
+        <v>0.003749999999999996</v>
       </c>
       <c r="N10" t="n">
         <v>20.75</v>
@@ -1899,7 +1899,7 @@
         <v>0.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0675</v>
+        <v>0.06749999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>21.50125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>57</v>
+      </c>
+      <c r="D75" t="n">
+        <v>36</v>
+      </c>
+      <c r="E75" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.0425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.919999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1872232764073372</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.111111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.579999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1745932415519398</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
